--- a/World-Builds/Donatism/Lexicon_Candidate_Index.xlsx
+++ b/World-Builds/Donatism/Lexicon_Candidate_Index.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,10 @@
     </font>
     <font>
       <name val="Arial"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -64,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -73,8 +77,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -966,7 +974,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Both hierarchies read "catholic" (universal) as their own rightful title; the Donatist sermon's own admonitio preserves a Donatist author mocking the Caecilianist use of the word as a hollow appropriation.</t>
+          <t>Both hierarchies read "catholic" (universal) as their own rightful title; Mabillon's own annotation on the Passio Donati sermon describes its Donatist author twisting the word into a sarcastic pun - "catholic" not as universal but as the place where wrongdoing is committed with impunity.</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1902,7 +1910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2356,40 +2364,44 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>Note: counts below are computed directly from the roster data at build time, not live formulas -- see build script comment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="n">
+    <row r="26">
+      <c r="A26" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="5">
-        <f>COUNTIF('Candidate Roster'!C2:C22,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="B26" s="6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="5">
-        <f>COUNTIF('Candidate Roster'!C2:C22,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="B27" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B27" s="5">
-        <f>COUNTIF('Candidate Roster'!C2:C22,3)</f>
-        <v/>
+      <c r="B28" s="6" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2403,7 +2415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2412,129 +2424,129 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Note: counts computed directly from roster data at build time, not live formulas (see build script).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Tag</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Terms</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>AS</t>
-        </is>
-      </c>
-      <c r="B2" s="2">
-        <f>COUNTIF('Candidate Roster'!D2:D22,"Y")</f>
-        <v/>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Traditor / Traditio; Reception without Reordination; Caecilianist; Church of the Martyrs; Deo laudes; Anniversaria Commemoratio; Primate / Primas; Agonistici (outsider alias: Circumcellion); Refusal of Imperial Legitimacy; Liber Regularum / The Seven Rules</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="B3" s="2">
-        <f>COUNTIF('Candidate Roster'!E2:E22,"Y")</f>
-        <v/>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Rebaptism (Rebaptizare); Purity (ministerial/sacramental); "Catholic" / Catholicus (contested application); Church / Ecclesia (the true-church claim); Schism; Martyr / Martyrdom (contested recognition); Confessor; Bishop / Episcopus (parallel hierarchy); Council / Concilium; Persecution (dual/layered memory)</t>
+          <t>Traditor / Traditio; Reception without Reordination; Caecilianist; Church of the Martyrs; Deo laudes; Anniversaria Commemoratio; Primate / Primas; Agonistici (outsider alias: Circumcellion); Refusal of Imperial Legitimacy; Liber Regularum / The Seven Rules</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="B4" s="2">
-        <f>COUNTIF('Candidate Roster'!F2:F22,"Y")</f>
-        <v/>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Traditor / Traditio; Rebaptism (Rebaptizare); Purity (ministerial/sacramental); "Donatist" / Pars Donati; Caecilianist; "Catholic" / Catholicus (contested application); Church / Ecclesia (the true-church claim); Schism; Martyr / Martyrdom (contested recognition); Confessor; Church of the Martyrs; Deo laudes; Bishop / Episcopus (parallel hierarchy); Agonistici (outsider alias: Circumcellion); Refusal of Imperial Legitimacy; Persecution (dual/layered memory)</t>
+          <t>Rebaptism (Rebaptizare); Purity (ministerial/sacramental); "Catholic" / Catholicus (contested application); Church / Ecclesia (the true-church claim); Schism; Martyr / Martyrdom (contested recognition); Confessor; Bishop / Episcopus (parallel hierarchy); Council / Concilium; Persecution (dual/layered memory)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>TC</t>
-        </is>
-      </c>
-      <c r="B5" s="2">
-        <f>COUNTIF('Candidate Roster'!G2:G22,"Y")</f>
-        <v/>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>16</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Traditor / Traditio; Rebaptism (Rebaptizare); Reception without Reordination; Purity (ministerial/sacramental); Anniversaria Commemoratio; Primate / Primas; Council / Concilium; Agonistici (outsider alias: Circumcellion); Liber Regularum / The Seven Rules</t>
+          <t>Traditor / Traditio; Rebaptism (Rebaptizare); Purity (ministerial/sacramental); "Donatist" / Pars Donati; Caecilianist; "Catholic" / Catholicus (contested application); Church / Ecclesia (the true-church claim); Schism; Martyr / Martyrdom (contested recognition); Confessor; Church of the Martyrs; Deo laudes; Bishop / Episcopus (parallel hierarchy); Agonistici (outsider alias: Circumcellion); Refusal of Imperial Legitimacy; Persecution (dual/layered memory)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="B6" s="2">
-        <f>COUNTIF('Candidate Roster'!H2:H22,"Y")</f>
-        <v/>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Traditor / Traditio; Rebaptism (Rebaptizare); Church / Ecclesia (the true-church claim); Martyr / Martyrdom (contested recognition); Church of the Martyrs; Deo laudes; Bishop / Episcopus (parallel hierarchy); Agonistici (outsider alias: Circumcellion)</t>
+          <t>Traditor / Traditio; Rebaptism (Rebaptizare); Reception without Reordination; Purity (ministerial/sacramental); Anniversaria Commemoratio; Primate / Primas; Council / Concilium; Agonistici (outsider alias: Circumcellion); Liber Regularum / The Seven Rules</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>PV</t>
-        </is>
-      </c>
-      <c r="B7" s="2">
-        <f>COUNTIF('Candidate Roster'!I2:I22,"Y")</f>
-        <v/>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>"Donatist" / Pars Donati; Martyr / Martyrdom (contested recognition); Agonistici (outsider alias: Circumcellion); Refusal of Imperial Legitimacy; Liber Regularum / The Seven Rules</t>
+          <t>Traditor / Traditio; Rebaptism (Rebaptizare); Church / Ecclesia (the true-church claim); Martyr / Martyrdom (contested recognition); Church of the Martyrs; Deo laudes; Bishop / Episcopus (parallel hierarchy); Agonistici (outsider alias: Circumcellion)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>"Donatist" / Pars Donati; Martyr / Martyrdom (contested recognition); Agonistici (outsider alias: Circumcellion); Refusal of Imperial Legitimacy; Liber Regularum / The Seven Rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="B8" s="2">
-        <f>COUNTIF('Candidate Roster'!J2:J22,"Y")</f>
-        <v/>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Agonistici (outsider alias: Circumcellion)</t>
         </is>
@@ -2551,7 +2563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2561,79 +2573,86 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Note: cross-check counts below are computed directly from roster data at build time, not live formulas (see build script).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>CT Tagged?</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Contest Type Specified in Doc_03 §4?</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Contest Type (summary)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Agonistici (outsider alias: Circumcellion)</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Meaning and historical scope: whether the hostile literary characterization of the group substantially reflects its actual character and scale, or is substantially a polemical construction (Frend vs. Shaw) - see Doc_03 §4 item 1.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Cross-check: CT-tagged terms in Candidate Roster</t>
         </is>
       </c>
-      <c r="B4" s="5">
-        <f>COUNTIF('Candidate Roster'!J2:J22,"Y")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="B5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>CT terms listed on this sheet</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Match?</t>
         </is>
       </c>
-      <c r="B6" s="5">
-        <f>IF(B4=B5,"OK","MISMATCH - investigate")</f>
-        <v/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/World-Builds/Donatism/Lexicon_Candidate_Index.xlsx
+++ b/World-Builds/Donatism/Lexicon_Candidate_Index.xlsx
@@ -589,12 +589,12 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Optatus (Registry row 2 - the Acta Purgationis Felicis and the wider Appendix of Documents, which Doc_02 §1 explicitly places inside this world's Author Gravity concentration despite its comparatively neutral, court-acts character, since Optatus chose what to include and how to frame it)</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Doc_02 §1</t>
+          <t>Doc_02 §1; Registry row 2</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>The name this world is remembered by, and the record is genuinely divided on its origin: Optatus's own quoted documents show Donatist clergy signing formal petitions "of the party of Donatus," yet Optatus turns that fact into an accusation - that they named a man instead of "the Church of Christ" - implying their own preferred self-description ran the other way.</t>
+          <t>The name this world is remembered by: Optatus's own quoted documents show Donatist clergy signing formal petitions "of the party of Donatus," but Optatus turns that very fact into an accusation - that they named a man instead of "the Church of Christ" - implying their own preferred self-description ran the other way.</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Agonistici (outsider alias: Circumcellion)</t>
+          <t>Agonistici (outsider alias: "Circumcellion")</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>"Contestants" - the self-designation Augustine himself reports for a rural, itinerant group independently attested in imperial legislation; "Circumcellion" is the label this world's opponents gave the same group, and is the word a modern participant will actually bring to the conversation.</t>
+          <t>"Contestants" - the self-designation Augustine reports for a rural, itinerant group whose bare existence is independently attested in imperial legislation; "Circumcellion" is the label this world's opponents gave the same group, and is the word a modern participant will actually bring to the conversation.</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Augustine/Optatus (HIGH on character/scale only)</t>
+          <t>Augustine/Optatus (HIGH - the group's character and scale, and the specific self-designation term itself, all reach this record only through Augustine's own report; only the group's bare existence is independently attested, via CTh 16.5.52, itself unvendored)</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Agonistici (outsider alias: Circumcellion)</t>
+          <t>Agonistici (outsider alias: "Circumcellion")</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Traditor / Traditio; Reception without Reordination; Caecilianist; Church of the Martyrs; Deo laudes; Anniversaria Commemoratio; Primate / Primas; Agonistici (outsider alias: Circumcellion); Refusal of Imperial Legitimacy; Liber Regularum / The Seven Rules</t>
+          <t>Traditor / Traditio; Reception without Reordination; Caecilianist; Church of the Martyrs; Deo laudes; Anniversaria Commemoratio; Primate / Primas; Agonistici (outsider alias: "Circumcellion"); Refusal of Imperial Legitimacy; Liber Regularum / The Seven Rules</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Traditor / Traditio; Rebaptism (Rebaptizare); Purity (ministerial/sacramental); "Donatist" / Pars Donati; Caecilianist; "Catholic" / Catholicus (contested application); Church / Ecclesia (the true-church claim); Schism; Martyr / Martyrdom (contested recognition); Confessor; Church of the Martyrs; Deo laudes; Bishop / Episcopus (parallel hierarchy); Agonistici (outsider alias: Circumcellion); Refusal of Imperial Legitimacy; Persecution (dual/layered memory)</t>
+          <t>Traditor / Traditio; Rebaptism (Rebaptizare); Purity (ministerial/sacramental); "Donatist" / Pars Donati; Caecilianist; "Catholic" / Catholicus (contested application); Church / Ecclesia (the true-church claim); Schism; Martyr / Martyrdom (contested recognition); Confessor; Church of the Martyrs; Deo laudes; Bishop / Episcopus (parallel hierarchy); Agonistici (outsider alias: "Circumcellion"); Refusal of Imperial Legitimacy; Persecution (dual/layered memory)</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Traditor / Traditio; Rebaptism (Rebaptizare); Reception without Reordination; Purity (ministerial/sacramental); Anniversaria Commemoratio; Primate / Primas; Council / Concilium; Agonistici (outsider alias: Circumcellion); Liber Regularum / The Seven Rules</t>
+          <t>Traditor / Traditio; Rebaptism (Rebaptizare); Reception without Reordination; Purity (ministerial/sacramental); Anniversaria Commemoratio; Primate / Primas; Council / Concilium; Agonistici (outsider alias: "Circumcellion"); Liber Regularum / The Seven Rules</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Traditor / Traditio; Rebaptism (Rebaptizare); Church / Ecclesia (the true-church claim); Martyr / Martyrdom (contested recognition); Church of the Martyrs; Deo laudes; Bishop / Episcopus (parallel hierarchy); Agonistici (outsider alias: Circumcellion)</t>
+          <t>Traditor / Traditio; Rebaptism (Rebaptizare); Church / Ecclesia (the true-church claim); Martyr / Martyrdom (contested recognition); Church of the Martyrs; Deo laudes; Bishop / Episcopus (parallel hierarchy); Agonistici (outsider alias: "Circumcellion")</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>"Donatist" / Pars Donati; Martyr / Martyrdom (contested recognition); Agonistici (outsider alias: Circumcellion); Refusal of Imperial Legitimacy; Liber Regularum / The Seven Rules</t>
+          <t>"Donatist" / Pars Donati; Martyr / Martyrdom (contested recognition); Agonistici (outsider alias: "Circumcellion"); Refusal of Imperial Legitimacy; Liber Regularum / The Seven Rules</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Agonistici (outsider alias: Circumcellion)</t>
+          <t>Agonistici (outsider alias: "Circumcellion")</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Agonistici (outsider alias: Circumcellion)</t>
+          <t>Agonistici (outsider alias: "Circumcellion")</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">

--- a/World-Builds/Donatism/Lexicon_Candidate_Index.xlsx
+++ b/World-Builds/Donatism/Lexicon_Candidate_Index.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Death borne for the true faith - but for this world's own most documented martyrs (the Macarian repression, 347-348), death at the hands of a rival Christian party's own imperial enforcement, a status the Caecilianist side never recognized as martyrdom at all.</t>
+          <t>Death borne for the true faith - but for this world's own most documented martyrs (the Macarian repression, 347–348), death at the hands of a rival Christian party's own imperial enforcement, a status the Caecilianist side never recognized as martyrdom at all.</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Not one persecution but (at least) two, held together in this world's own memory: the empire-wide Diocletianic persecution suffered alongside the eventual rival, and the later, specifically Macarian persecution (347-348) suffered at that rival's own instigation.</t>
+          <t>Not one persecution but (at least) two, held together in this world's own memory: the empire-wide Diocletianic persecution suffered alongside the eventual rival, and the later, specifically Macarian persecution (347–348) suffered at that rival's own instigation.</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
